--- a/results/scraped_Cape_Town_Sports_and_Recreation.xlsx
+++ b/results/scraped_Cape_Town_Sports_and_Recreation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="229">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -43,24 +43,21 @@
     <t>YahooSports: News, Scores, Video, Fantasy Games, Schedules</t>
   </si>
   <si>
+    <t>Sports: LatestSportsNews &amp;SportsArticles | AP News</t>
+  </si>
+  <si>
+    <t>MSNSports</t>
+  </si>
+  <si>
+    <t>ESPN - ServingSportsFans. Anytime. Anywhere.</t>
+  </si>
+  <si>
+    <t>CBSSports- News, Live Scores, Schedules, Fantasy Games, Video …</t>
+  </si>
+  <si>
     <t>Latest IowaSportsNews &amp; Game Analysis | The Des Moines Register</t>
   </si>
   <si>
-    <t>Sports: LatestSportsNews &amp;SportsArticles | AP News</t>
-  </si>
-  <si>
-    <t>NFL News, Scores, Standings, Schedules, Videos and more -Yahoo Sports</t>
-  </si>
-  <si>
-    <t>MSNSports</t>
-  </si>
-  <si>
-    <t>ESPN - ServingSportsFans. Anytime. Anywhere.</t>
-  </si>
-  <si>
-    <t>CBSSports- News, Live Scores, Schedules, Fantasy Games, Video …</t>
-  </si>
-  <si>
     <t>BBC Sport- Scores, Fixtures, News - Live Sport</t>
   </si>
   <si>
@@ -163,7 +160,7 @@
     <t>NFL.com | Official Site of the NationalFootballLeague</t>
   </si>
   <si>
-    <t>NFLSchedules: Games, Times, Matchups &amp; Tickets</t>
+    <t>NFLNews | LatestNFL FootballNews |NFL.com</t>
   </si>
   <si>
     <t>Football- Wikipedia</t>
@@ -175,19 +172,19 @@
     <t>Scores &amp; Fixtures-Football-BBC Sport</t>
   </si>
   <si>
+    <t>Football- latest news today, results &amp; video highlights - BBC</t>
+  </si>
+  <si>
     <t>FootballGames, Results, Scores, Transfers, News |Sky Sports</t>
   </si>
   <si>
-    <t>Football- latest news today, results &amp; video highlights - BBC</t>
-  </si>
-  <si>
     <t>NFL News, Scores, Stats, Standings and Rumors - NationalFootball...</t>
   </si>
   <si>
-    <t>CollegeFootballonESPN- Scores, Stats and Highlights</t>
-  </si>
-  <si>
-    <t>NFL News, Scores, Standings, Schedules, Videos and more -Yahoo…</t>
+    <t>American football- Wikipedia</t>
+  </si>
+  <si>
+    <t>ESPN - Serving Sports Fans. Anytime. Anywhere.</t>
   </si>
   <si>
     <t>SocceronESPN- Scores, Stats and Highlights</t>
@@ -229,16 +226,16 @@
     <t>World Rugby</t>
   </si>
   <si>
-    <t>Home | SARugby</t>
+    <t>Fixtures and Results |World Rugby</t>
   </si>
   <si>
     <t>Rugby Union- latest news today, results &amp; video -BBC Sport</t>
   </si>
   <si>
-    <t>Rugby football- Wikipedia</t>
-  </si>
-  <si>
-    <t>Fixtures and Results |World Rugby</t>
+    <t>Rugby101 - How the Sport Works | USARugby</t>
+  </si>
+  <si>
+    <t>RugbyUpcoming - SuperSport</t>
   </si>
   <si>
     <t>PlanetRugby| News, Live Scores, Fixtures, Results &amp; Stats</t>
@@ -247,7 +244,7 @@
     <t>Rugby|RugbyUnion | The Home ofRugby| RugbyPass</t>
   </si>
   <si>
-    <t>Rugby101 - How the Sport Works | USARugby</t>
+    <t>Scores &amp; Fixtures-RugbyUnion - BBC Sport</t>
   </si>
   <si>
     <t>CricketWireless | Unlimited Phone Plans | Affordable Cell Phones | No ...</t>
@@ -259,55 +256,55 @@
     <t>Cricket- Wikipedia</t>
   </si>
   <si>
-    <t>Manage Account |CricketWireless</t>
+    <t>LiveCricketScores | Today's Match Scorecard &amp; Ball-by-Ball …</t>
+  </si>
+  <si>
+    <t>Quick PayPage -CricketWireless</t>
+  </si>
+  <si>
+    <t>DoodleCricket– Play Google DoodleCricketGame Free</t>
+  </si>
+  <si>
+    <t>LiveCricketScores - Find Latest Scores of all Matches Online - ESPN</t>
   </si>
   <si>
     <t>Cricket– Ashes, Test, T20 &amp; ODI news, scores &amp; results - BBC</t>
   </si>
   <si>
+    <t>Cricket| Definition, Origin, History, Equipment, Gameplay, Rules ...</t>
+  </si>
+  <si>
     <t>Home |cricket.com.au</t>
   </si>
   <si>
-    <t>LiveCricketScores | Today's Match Scorecard &amp; Ball-by-Ball …</t>
-  </si>
-  <si>
-    <t>RecentCricketResults &amp; Scorecards | IPL 2026 | Cricbuzz</t>
-  </si>
-  <si>
-    <t>Scores &amp; Fixtures -Cricket- BBC Sport</t>
-  </si>
-  <si>
-    <t>Cricket| Definition, Origin, History, Equipment, Gameplay, Rules ...</t>
-  </si>
-  <si>
-    <t>Swim Lessons inHouston,HoustonSwim Club Swim School</t>
-  </si>
-  <si>
-    <t>14Best Houston Area Swimming Holes-TexasWanderers</t>
-  </si>
-  <si>
-    <t>12 Fantastic Places To Swim InHoustonAnd Beyond</t>
-  </si>
-  <si>
-    <t>11 BestSwimmingHoles &amp; Lakes to Swim inHouston</t>
-  </si>
-  <si>
-    <t>18SwimmingHoles inHouston,Texasfor a Fun Swim</t>
-  </si>
-  <si>
-    <t>ShAC - SwimHoustonAquatics Center</t>
-  </si>
-  <si>
-    <t>SwimmingPrograms | YMCA of GreaterHouston</t>
-  </si>
-  <si>
-    <t>GulfSwimmingLSC Home - SportsEngine</t>
-  </si>
-  <si>
-    <t>SwimmingLessons in NYC &amp; ClassesHouston| SwimJim, Inc</t>
-  </si>
-  <si>
-    <t>Harris CountyAquatics Program - Rodney Ellis</t>
+    <t>SwimmingLessons - Saint PaulMinnesota</t>
+  </si>
+  <si>
+    <t>Swimming- Wikipedia</t>
+  </si>
+  <si>
+    <t>Aquatics- Saint PaulMinnesota</t>
+  </si>
+  <si>
+    <t>SwimmingLessons inSt. Paul,Minnesota-Foss Swim School</t>
+  </si>
+  <si>
+    <t>Swimming| Sport, Olympics, Definition, History, Strokes, &amp; Facts ...</t>
+  </si>
+  <si>
+    <t>STAR Swim Team Home - SportsEngine</t>
+  </si>
+  <si>
+    <t>Best Twin Cities Water Parks: 15 Spots for Family Fun (2026)</t>
+  </si>
+  <si>
+    <t>Indoor Waterparks and Pools- Best Places to Swim in the Twin Cities,MN</t>
+  </si>
+  <si>
+    <t>Gopher Swim School | Recreation and Wellness</t>
+  </si>
+  <si>
+    <t>Aquatics Overview -MinnesotaJCC</t>
   </si>
   <si>
     <t>TennisScores, Tournaments, Rankings &amp; News</t>
@@ -319,25 +316,52 @@
     <t>Official Site of Men's ProfessionalTennis|ATP Tour|Tennis</t>
   </si>
   <si>
+    <t>Tennis- Wikipedia</t>
+  </si>
+  <si>
     <t>TennisLive Scores,TennisResults - ATP, WTA | Flashscore.com</t>
   </si>
   <si>
-    <t>Tennis- Wikipedia</t>
+    <t>TennisonESPN- Scores, Schedule and News</t>
+  </si>
+  <si>
+    <t>Tournaments |ATP Tour|Tennis</t>
   </si>
   <si>
     <t>Tennis- Scores, Results &amp; Latest News -BBC Sport</t>
   </si>
   <si>
-    <t>Tournaments |ATP Tour|Tennis</t>
-  </si>
-  <si>
-    <t>TennisonESPN- Scores, Schedule and News</t>
-  </si>
-  <si>
     <t>TennisTournaments</t>
   </si>
   <si>
-    <t>The Official Home of the Women'sTennisAssociation | WTATennis</t>
+    <t>Scores &amp; Schedule -Tennis- BBC Sport</t>
+  </si>
+  <si>
+    <t>Download and install Google Chrome</t>
+  </si>
+  <si>
+    <t>webstore - Chrome Web Store - Stack Overflow</t>
+  </si>
+  <si>
+    <t>How to link to chrome extension like Chrome Web Store?</t>
+  </si>
+  <si>
+    <t>Install &amp; manage web apps - Chrome Web Store Help</t>
+  </si>
+  <si>
+    <t>拡張機能をインストールして管理する - Chrome ウェブストア ヘルプ</t>
+  </si>
+  <si>
+    <t>Google Chrome Help</t>
+  </si>
+  <si>
+    <t>Install and manage extensions - Chrome Web Store Help</t>
+  </si>
+  <si>
+    <t>Fazer o download e instalar o Google Chrome</t>
+  </si>
+  <si>
+    <t>What is the Chrome Web Store? - Google Help</t>
   </si>
   <si>
     <t>Sports &amp; Recreation</t>
@@ -346,307 +370,334 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=032ed67db491c7bf549a94447179c7dd3a65c9b1aaaaf3b9b1c585ac8429561aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec29d2-df1d-6f39-12ad-3e30de3c6e3b&amp;u=a1aHR0cHM6Ly9zcG9ydHMueWFob28uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6833f0f5f40f63eba6fb3a3d1171c064a899c6b295d2ccebd989ac5d5e30ec9cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec29d2-df1d-6f39-12ad-3e30de3c6e3b&amp;u=a1aHR0cHM6Ly93d3cuZGVzbW9pbmVzcmVnaXN0ZXIuY29tL3Nwb3J0cy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9f6fa45c97469450429ac2c486f59f139a5c7bd4cd0c2ec34ea7fd0a93afe91fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec29d2-df1d-6f39-12ad-3e30de3c6e3b&amp;u=a1aHR0cHM6Ly9hcG5ld3MuY29tL3Nwb3J0cw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=529ba72c6300574ef3e5010cb2a7c79887eb9a0cc6508511e5d13a5e8955606dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec29d2-df1d-6f39-12ad-3e30de3c6e3b&amp;u=a1aHR0cHM6Ly9zcG9ydHMueWFob28uY29tL25mbC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e1165633048774cfc26f893811e92ffbae8b33ceff6e7cd142e5e3899763b0abJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec29d2-df1d-6f39-12ad-3e30de3c6e3b&amp;u=a1aHR0cHM6Ly93d3cubXNuLmNvbS9lbi11cy9zcG9ydHM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9a191b4f0aa17b95f8e77ef3fc444b5b3ee136a49936d5468ae0debb7a4ab02bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec29d2-df1d-6f39-12ad-3e30de3c6e3b&amp;u=a1aHR0cHM6Ly93d3cuZXNwbi5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=11776b4c2bd4eadcdbd93556dfa7a2655f82918d824f6f89618beb3f5d79611aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec29d2-df1d-6f39-12ad-3e30de3c6e3b&amp;u=a1aHR0cHM6Ly93d3cuY2Jzc3BvcnRzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=219ce4b53e4db171a9a015b7da28c29466b330cfbe877b44ce6e4354822c3c70JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec29d2-df1d-6f39-12ad-3e30de3c6e3b&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvbS9zcG9ydA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87ee41a1357841aa2f2c9dd707aa26b56c07ab571ce864ac5a7867bf7e8351adJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec29d2-df1d-6f39-12ad-3e30de3c6e3b&amp;u=a1aHR0cHM6Ly93d3cuZm94c3BvcnRzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=809231856a4476d9446fd8eb3358b5816eb363882d5ecca09a7addb79a3caef0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec29d2-df1d-6f39-12ad-3e30de3c6e3b&amp;u=a1aHR0cHM6Ly93d3cudXNhdG9kYXkuY29tL3Nwb3J0cy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=536e858ee9a1839c71d97a1f9474d0eab25cded37933182589d24bad259a7aa8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21bdcc10-0a3e-6720-38f3-dbf20b9a66af&amp;u=a1aHR0cHM6Ly93d3cucmVjcmVhdGlvbi5nb3Yv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e98d22170230da3a4a64acac85812508bf7962aa69756fae774f9b9cac63a27dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21bdcc10-0a3e-6720-38f3-dbf20b9a66af&amp;u=a1aHR0cHM6Ly93d3cuY2l0eW9mZWFzdGxhbnNpbmcuY29tLzI1NzEvUGFya3MtUmVjcmVhdGlvbi1BcnRz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=02641ee4dbc8e5a2c2c47abc8944c0eca03e1d7826969a2e1f7fc8e6d3add607JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21bdcc10-0a3e-6720-38f3-dbf20b9a66af&amp;u=a1aHR0cHM6Ly9yZWNyZWF0aW9uLnVtaWNoLmVkdS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b40db892c5a962f6fdb9a77c0bdea50876d11a3f3bc962ae79dfd3addb971ca8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21bdcc10-0a3e-6720-38f3-dbf20b9a66af&amp;u=a1aHR0cHM6Ly93d3cuY2l0eW9mZWFzdGxhbnNpbmcuY29tLzg2MS9Qcm9ncmFtcy1BY3Rpdml0aWVz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9ecd424544b5f8edfe7532d0a1cf25c59bda07acf75d42d9469858fd0296e977JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21bdcc10-0a3e-6720-38f3-dbf20b9a66af&amp;u=a1aHR0cHM6Ly93d3cucmVjcmVhdGlvbi5nb3YvbG9nLWlu&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d27b1d8d33af459a0ebb4c3b8049c7342d3206b9a25b6d9eaa37036cebbc08aaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21bdcc10-0a3e-6720-38f3-dbf20b9a66af&amp;u=a1aHR0cHM6Ly9yZWNzcG9ydHMubXN1LmVkdS9mYWNpbGl0aWVzL3N0dWRlbnQtcmVjcmVhdGlvbi1hbmQtd2VsbG5lc3MtY2VudGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1529d290ab7bf7d03013ed744f55be6692a8fa3f2bf77e2f44e49757944a490cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21bdcc10-0a3e-6720-38f3-dbf20b9a66af&amp;u=a1aHR0cHM6Ly93d3cubGFuc2luZy5vcmcvdGhpbmdzLXRvLWRvL291dGRvb3ItcmVjcmVhdGlvbi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5dc8b79dd49cd2896af846c5007867e2a0f9d1d25711f8349d6c2f64957286acJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21bdcc10-0a3e-6720-38f3-dbf20b9a66af&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvUmVjcmVhdGlvbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d9c70163bc99254faa0c693c807d88291bc7bc553df88fd34d21ea49f46be90cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21bdcc10-0a3e-6720-38f3-dbf20b9a66af&amp;u=a1aHR0cHM6Ly93d3cubGFuc2luZ21pLmdvdi9wYXJrcy1yZWNyZWF0aW9u&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=60ddf5dd01a5a37f2c17f0431fc72d9a073d2b15766eb07d1159be3a46f65f97JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21bdcc10-0a3e-6720-38f3-dbf20b9a66af&amp;u=a1aHR0cHM6Ly93d3cubGFuc2luZy5vcmcvdGhpbmdzLXRvLWRvL291dGRvb3ItcmVjcmVhdGlvbi9wYXJrcy1hbmQtZ2FyZGVucy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2ebc5c345e6e8b2f984dc517193861d241fbf86e4f67e9790c508be2b27c836bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b8ac6b-7157-6c9f-33dc-bb8970516da5&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQzNTk0OTIyNi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=24e515505191e30c671933d5dc7ceb4246f6da150a78f0d1db70d60fc0c567e7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b8ac6b-7157-6c9f-33dc-bb8970516da5&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvWW91dGg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=20dfe1ff09c4dee988a66b18049995a808be245be541d1cfc0bfba7d735db975JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b8ac6b-7157-6c9f-33dc-bb8970516da5&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1Yd3VETVNsRXJraw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=59e33bd31188e01183d0124052446b08fb3fefb2d8ec566607896ef3571bc2f6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b8ac6b-7157-6c9f-33dc-bb8970516da5&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQzODY5Mzg4OC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=db765577356172f900092398d22c5f2b043a3ea6edea13514313bf6ef8d70a45JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b8ac6b-7157-6c9f-33dc-bb8970516da5&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3lvdXRo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fa0e39fc01eaef922173db2475ec66a3e94b648fb701aa072a68d36b87ec4168JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b8ac6b-7157-6c9f-33dc-bb8970516da5&amp;u=a1aHR0cHM6Ly93d3cudHZpbnNpZGVyLmNvbS8xMjg0MDAzL3lvdXRoLXByZW1pZXJlLWRhdGUtdHJhaWxlci1jYXN0LXBsb3Qv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=36fb34ca113feac10db1fd30500a2194614558535129eba1db3efa6c4832ce78JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b8ac6b-7157-6c9f-33dc-bb8970516da5&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvWW91dGhfKFRWX3Nlcmllcyk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3c66f50648a4b0d0e858345a2f5e09f4da5d4b2e9e5e463281f4756b703bdfa3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b8ac6b-7157-6c9f-33dc-bb8970516da5&amp;u=a1aHR0cHM6Ly95b3V0aC5nb3Yv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d5bc5e539fa6fde9456fafb1248f6060a1c178664a2d4405ecaf4abc42eed7b2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b8ac6b-7157-6c9f-33dc-bb8970516da5&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj0yeGh0Q19pV2NnWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dc2b8c4ab4f8e61121e1a8b4302980922a3b5b1daa37ff1edd1db6cf6d3dc19bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b8ac6b-7157-6c9f-33dc-bb8970516da5&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3lvdXRo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d311a2a4c6ea07187641d488369ebc595612c09326674d91083a2b5918438503JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c7ec95b-ad32-6f45-0016-deb9ac5f6e78&amp;u=a1aHR0cHM6Ly93d3cubWxiLmNvbS9hdGhsZXRpY3M_bXNvY2tpZD0xYzdlYzk1YmFkMzI2ZjQ1MDAxNmRlYjlhYzVmNmU3OA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e06199205367318e0acfd987bf88916d43be0877b82f5f745a9392fac87eb33fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c7ec95b-ad32-6f45-0016-deb9ac5f6e78&amp;u=a1aHR0cHM6Ly93d3cuYXRobGV0aWMubmV0Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4110e9b5bd9b9860a408381f6be01ac48ad4e49dd0601a5c9fa4f050960632efJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c7ec95b-ad32-6f45-0016-deb9ac5f6e78&amp;u=a1aHR0cHM6Ly93b3JsZGF0aGxldGljcy5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e298237b78b114f78f9cd484242c9ad3ebc7d68e496c1e8e764a2c390e85f613JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c7ec95b-ad32-6f45-0016-deb9ac5f6e78&amp;u=a1aHR0cHM6Ly93d3cubnl0aW1lcy5jb20vYXRobGV0aWMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=35a1a40718fde27fb4b06e7363b3c5dfb112077af4d6fad2294e26582caf7bedJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c7ec95b-ad32-6f45-0016-deb9ac5f6e78&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQXRobGV0aWNzXyhiYXNlYmFsbCk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1151488403c723375407f49c602a64485597bb2e4bc39d02515af710807d9e5aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c7ec95b-ad32-6f45-0016-deb9ac5f6e78&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU3BvcnRfb2ZfQXRobGV0aWNz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=494d72229238cc2e48a2640e79fb0e977ca4f752a6e37aa8a5e74af1691c82bfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c7ec95b-ad32-6f45-0016-deb9ac5f6e78&amp;u=a1aHR0cHM6Ly93d3cuZXNwbi5jb20vbWxiL3RlYW0vXy9uYW1lL2F0aC9hdGhsZXRpY3M&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6de6291abccf7296da1b80594639adaf46466be17e96ff42ac827ad6dd80244aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c7ec95b-ad32-6f45-0016-deb9ac5f6e78&amp;u=a1aHR0cHM6Ly93d3cuZXNwbi5jb20vYXRobGV0aWNzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=73efcb845b8b4fdc33a9704d332cf2c0fb4a84b9804e5771e8c3090782ca1efdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c7ec95b-ad32-6f45-0016-deb9ac5f6e78&amp;u=a1aHR0cHM6Ly93d3cubWxiLmNvbS9hdGhsZXRpY3MvbmV3cz9tc29ja2lkPTFjN2VjOTViYWQzMjZmNDUwMDE2ZGViOWFjNWY2ZTc4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=959d115ecb6c29132ac58db5fac40eefb4c8d0dc199fd25ce2217126aba08ad0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c7ec95b-ad32-6f45-0016-deb9ac5f6e78&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc3BvcnRzL2F0aGxldGljcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ceaa90ab4254654e32271dfcc440d54c35272729c07461d1f0ce13b873034c06JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c5992d9-28b3-695f-28b9-853b29f868e2&amp;u=a1aHR0cHM6Ly93d3cubmZsLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb197473ce0c8fd34335cbf5c5c41703271d35108e83b7451b5af73bd3bfeadcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c5992d9-28b3-695f-28b9-853b29f868e2&amp;u=a1aHR0cHM6Ly93d3cubmZsLmNvbS9zY2hlZHVsZXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=23c57212097485b5ea6687e96fa133f3f4ac97893ed3c6332380426edf42d8c3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c5992d9-28b3-695f-28b9-853b29f868e2&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRm9vdGJhbGw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c7f1bd125534f5c2a8994d49492defab115927b3766c0ad7ace573661ba81a66JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c5992d9-28b3-695f-28b9-853b29f868e2&amp;u=a1aHR0cHM6Ly93d3cuZXNwbi5jb20vbmZsLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2938766425939375c6ef4aba741216fccca5587505802ee484c0cad133d45e9eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c5992d9-28b3-695f-28b9-853b29f868e2&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2Zvb3RiYWxsL3Njb3Jlcy1maXh0dXJlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bec1c0a54f15b15ae844fa3d20e63ad858253d7d3b27b37f2f8da1fd7ad6ff7bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c5992d9-28b3-695f-28b9-853b29f868e2&amp;u=a1aHR0cHM6Ly93d3cuc2t5c3BvcnRzLmNvbS9mb290YmFsbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=557f066758dc4eecf3763530d953bfbcd538e0bdc6389da9faa11ba58ea7343dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c5992d9-28b3-695f-28b9-853b29f868e2&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2Zvb3RiYWxs&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5d0a9b49eaaa68278751f0baf8ee1bf09e79b2209614a9f97b90f1f8bcf0779fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c5992d9-28b3-695f-28b9-853b29f868e2&amp;u=a1aHR0cHM6Ly93d3cuY2Jzc3BvcnRzLmNvbS9uZmwv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5019661f77211e66c6ca6909f9499e4afae1fab2701e7885ffdf79eeb79db022JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c5992d9-28b3-695f-28b9-853b29f868e2&amp;u=a1aHR0cHM6Ly93d3cuZXNwbi5jb20vY29sbGVnZS1mb290YmFsbC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2b0875b0e9c04293ad2ada1cd844a06886dc7618a13043daa66b64085fd73279JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c5992d9-28b3-695f-28b9-853b29f868e2&amp;u=a1aHR0cHM6Ly9zcG9ydHMueWFob28uY29tL25mbC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fc18da41ca509c855f1b4181a09180760e9b61f6c059535e86c19a42fc7ca0a9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=131d7947-8e02-61de-2ec9-6ea58fef6066&amp;u=a1aHR0cHM6Ly93d3cuZXNwbi5jb20vc29jY2VyLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2cda7ffba43666b06a2e4286931084f1d8f47f8963937ad0633da0b10f26d947JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=131d7947-8e02-61de-2ec9-6ea58fef6066&amp;u=a1aHR0cHM6Ly93d3cuZXNwbi5jb20vc29jY2VyL3Njb3JlYm9hcmQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0d3ebb4c94030fcaa457898af2a1894bcd10f1bd3a86e05d1be2a9997f4253e5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=131d7947-8e02-61de-2ec9-6ea58fef6066&amp;u=a1aHR0cHM6Ly93d3cuZWxnaW55b3V0aHNvY2Nlci5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=91ca5098339bbc03186c3a13be4932bb51b85b7392587a55c7eebb1d3537f3c6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=131d7947-8e02-61de-2ec9-6ea58fef6066&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Bc3NvY2lhdGlvbl9mb290YmFsbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bc1dd1aa0be1b97ccc14c4385d7eed987facd1cf1da856b9105dadc31ce02581JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=131d7947-8e02-61de-2ec9-6ea58fef6066&amp;u=a1aHR0cHM6Ly93d3cubGl2ZXNjb3JlLmNvbS9lbi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b2a6d3b2ce532d7cbb3d69454bad89a57144c97bed1e25d49c9f260cf7ac59c5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=131d7947-8e02-61de-2ec9-6ea58fef6066&amp;u=a1aHR0cHM6Ly93d3cuZmxhc2hzY29yZS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=37bca029797ae0e3e0065f2a067417951a0f39cb0f91c8a59dcf5fa9fb1a9497JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=131d7947-8e02-61de-2ec9-6ea58fef6066&amp;u=a1aHR0cHM6Ly93d3cuZmlmYS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=421db89da5ae185e4e2eaa325e4719919f5c4de58d2e1944b5d2e402441747aeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=131d7947-8e02-61de-2ec9-6ea58fef6066&amp;u=a1aHR0cHM6Ly93d3cubWxzc29jY2VyLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=20bbef5c76e78224ea12969274a73a319a8bf256e5247ddc8d5bc0b7504783d7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=131d7947-8e02-61de-2ec9-6ea58fef6066&amp;u=a1aHR0cHM6Ly91cy5zb2NjZXJ3YXkuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=829ca3647fbe74ccf0de3d3320e36734ba82ebfb8288e61bcb8bff8b7c013235JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=131d7947-8e02-61de-2ec9-6ea58fef6066&amp;u=a1aHR0cHM6Ly93d3cuYmVzb2NjZXIuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cf56ca839d12dca19fa2f70c501c0c58461b746cc8222333e7265814553f8dcbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f5c58b0-a6c6-6233-0208-4f52a76263e7&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvUnVnYnlfdW5pb24&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6dfa513c2b5c4777c09614da2af50e9738eeb91dc690ae71924abf2f075cd98bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f5c58b0-a6c6-6233-0208-4f52a76263e7&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc3BvcnRzL3J1Z2J5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=667a9b3497c09230fa590e0208ebbfd5af7fcf3deda5771a27cee9b177c93ab3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f5c58b0-a6c6-6233-0208-4f52a76263e7&amp;u=a1aHR0cHM6Ly93d3cud29ybGQucnVnYnkv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=67a1fe94daadb75e28bc62f369f3d8885fc1403b51fafdcefe1c6012307b494bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f5c58b0-a6c6-6233-0208-4f52a76263e7&amp;u=a1aHR0cHM6Ly9zcHJpbmdib2tzLnJ1Z2J5Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4e100db2f16b6cfaa9bb7c1793624a4eb05db5b7f72ccbd4a14b36827aaf8ec3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f5c58b0-a6c6-6233-0208-4f52a76263e7&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L3J1Z2J5LXVuaW9u&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a5f639625e2fe272aaf3ca122391a70b9fed91c13233fdfe743365a350900148JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f5c58b0-a6c6-6233-0208-4f52a76263e7&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvUnVnYnlfZm9vdGJhbGw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c1468db374f773e6580960e36c96ab25baac55f1b9bcb7ee51033adc18e0df3eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f5c58b0-a6c6-6233-0208-4f52a76263e7&amp;u=a1aHR0cHM6Ly93d3cud29ybGQucnVnYnkvdG91cm5hbWVudHMvZml4dHVyZXMtcmVzdWx0cw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eceae8eee341038ade82c272422684eaabd35fb669d0cc35407ed4693973e08fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f5c58b0-a6c6-6233-0208-4f52a76263e7&amp;u=a1aHR0cHM6Ly93d3cucGxhbmV0cnVnYnkuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=64b3774255a3970aa86a967a50367a55532128c5257d8a47bcc800b7a85cd4b2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f5c58b0-a6c6-6233-0208-4f52a76263e7&amp;u=a1aHR0cHM6Ly93d3cucnVnYnlwYXNzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6885e6e58ad94f3084fb8ee54ac04679bcf729f424a2e8be2af6833b8329f1b6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f5c58b0-a6c6-6233-0208-4f52a76263e7&amp;u=a1aHR0cHM6Ly91c2EucnVnYnkvcnVnYnkxMDE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a359057ed6966d0ba075d1711929a5541cd474d4cc934bceb6067a0d8f31f9ebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38618fc1-5758-64af-0eea-982356fc65a4&amp;u=a1aHR0cHM6Ly93d3cuY3JpY2tldHdpcmVsZXNzLmNvbS8_bXNvY2tpZD0zODYxOGZjMTU3NTg2NGFmMGVlYTk4MjM1NmZjNjVhNA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9a9513a688cce2d913abd4ab036cec401ce2a94c513f41ea959e47818ca4a587JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38618fc1-5758-64af-0eea-982356fc65a4&amp;u=a1aHR0cHM6Ly93d3cuY3JpY2luZm8uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=748c4cc7bc453dc2735824ff3b8ae558f0787484dbd5b7eee237c52e5941174aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38618fc1-5758-64af-0eea-982356fc65a4&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ3JpY2tldA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d3fa7f697412252f604456a7642e0e44e644dc120c749dd22159e502425ae498JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38618fc1-5758-64af-0eea-982356fc65a4&amp;u=a1aHR0cHM6Ly93d3cuY3JpY2tldHdpcmVsZXNzLmNvbS9tYW5hZ2VhY2NvdW50P21zb2NraWQ9Mzg2MThmYzE1NzU4NjRhZjBlZWE5ODIzNTZmYzY1YTQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6fe6e01eef2043aa245c0d0fa49891fbb3617fb005a1c88b511d9f416b175848JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38618fc1-5758-64af-0eea-982356fc65a4&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2NyaWNrZXQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=519b04e5c9fd763f553f936bf8a381ecb4edccbe1f9b120665cf25f5338af4a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38618fc1-5758-64af-0eea-982356fc65a4&amp;u=a1aHR0cHM6Ly93d3cuY3JpY2tldC5jb20uYXUv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c4a3750c2b3e29d32d8a447e03d37d7cea09c32a7b99cc31195c7d58142c561bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38618fc1-5758-64af-0eea-982356fc65a4&amp;u=a1aHR0cHM6Ly93d3cuY3JpY2luZm8uY29tL2xpdmUtY3JpY2tldC1zY29yZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a6447daff5e08e7bddbaf338e60b8587cd90c7d9c7b4deff1ca7bcf91c57dfddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38618fc1-5758-64af-0eea-982356fc65a4&amp;u=a1aHR0cHM6Ly93d3cuY3JpY2J1enouY29tL2NyaWNrZXQtbWF0Y2gvbGl2ZS1zY29yZXMvcmVjZW50LW1hdGNoZXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=22e6043b7e5374767c317c78455a8286fce470350cffc6c757696c381c0df5a1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38618fc1-5758-64af-0eea-982356fc65a4&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2NyaWNrZXQvc2NvcmVzLWZpeHR1cmVz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5db59ed0d01db29d409d47847e55fbd253e4846cbbea097afc13e2a581aa26a6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38618fc1-5758-64af-0eea-982356fc65a4&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc3BvcnRzL2NyaWNrZXQtc3BvcnQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d3fb83a57aae452d1a1e407cdc600a4bb9cea5ac40a7c3930f2603c0bbe0a6b2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136fe8fa-9997-6435-3442-ff1898f665e8&amp;u=a1aHR0cHM6Ly93d3cuaG91c3RvbnN3aW1jbHViLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c5a0ca907fee024daeec578622792859fdb9771fcf9bb0afcf8a34f8a6d6a6fbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136fe8fa-9997-6435-3442-ff1898f665e8&amp;u=a1aHR0cHM6Ly90ZXhhc3dhbmRlcmVycy5jb20vMTItYmVzdC1ob3VzdG9uLWFyZWEtc3dpbW1pbmctaG9sZXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=66a4d7a4b3b2da707f9a05e93cb91019ec1a28014b0b416ba80eca7f35cc9389JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136fe8fa-9997-6435-3442-ff1898f665e8&amp;u=a1aHR0cHM6Ly9zZWNyZXRob3VzdG9uLmNvbS9wbGFjZXMtdG8tc3dpbS1pbi1ob3VzdG9uLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=feaa1b087e6cf72ad1381378e484fda81521c2be1d58930d54f10725196c37b2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136fe8fa-9997-6435-3442-ff1898f665e8&amp;u=a1aHR0cHM6Ly9nb3dhbmRlcmx5LmNvbS9zd2ltbWluZy1pbi1ob3VzdG9uLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=303794cb9a7d18b9781814388ff74ffdfd34ea9679b028e98ff7afa03829a6ddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136fe8fa-9997-6435-3442-ff1898f665e8&amp;u=a1aHR0cHM6Ly93d3cuaG91c3Rvbm9udGhlY2hlYXAuY29tL3N3aW1taW5nLWhvbGVzLWluLWhvdXN0b24v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b00dcfd8bd5abc7e1d7c0a7e0e95c48b11f5d786488b43b2a97b557a9d941c76JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136fe8fa-9997-6435-3442-ff1898f665e8&amp;u=a1aHR0cHM6Ly93d3cuc3dpbXNoYWMuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d802d638886f920b0de69388259bb93459614d050f3d8135d7e8841dacc0a7dbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136fe8fa-9997-6435-3442-ff1898f665e8&amp;u=a1aHR0cHM6Ly95bWNhaG91c3Rvbi5vcmcvcHJvZ3JhbXMvc3dpbW1pbmc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=382586d10e245be713557601242fdef17c7b204f79a710b036e9a6c5ced9ee5bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136fe8fa-9997-6435-3442-ff1898f665e8&amp;u=a1aHR0cHM6Ly93d3cuZ29tb3Rpb25hcHAuY29tL3RlYW0vZ3Nsc2MvcGFnZS9ob21l&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0f87a6d3af09933d75fc238b496f78d768f2ca3a970a40c9893710b0912e51b5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136fe8fa-9997-6435-3442-ff1898f665e8&amp;u=a1aHR0cHM6Ly93d3cuc3dpbWppbS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=69b6da6d6d09d78e4b14d4a85fdc4e3155c7991d45bebe1503daa11c40a53846JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136fe8fa-9997-6435-3442-ff1898f665e8&amp;u=a1aHR0cHM6Ly93d3cuaGNwMS5uZXQvQXF1YXRpY3M&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8a70aaeb24c56d65f9bf8d4fd65c2714d532cce837415fd07e2a59a169498a1aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13b427e6-f759-61ce-3736-3004f6ef6064&amp;u=a1aHR0cHM6Ly93d3cudGVubmlzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=71ecf6998ffb70fb0774fb4b1fb29477881f5ae00090b4e95de29d4b8a751c2bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13b427e6-f759-61ce-3736-3004f6ef6064&amp;u=a1aHR0cHM6Ly93d3cuZXNwbi5jb20vdGVubmlzL3Njb3JlYm9hcmQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=47e5b3c1f43d4a7dfc0b5d8e608190d8de740d5a90cf095fbd52738c0021be40JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13b427e6-f759-61ce-3736-3004f6ef6064&amp;u=a1aHR0cHM6Ly93d3cuYXRwdG91ci5jb20vZW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=babf23fc950ae593cca4e51c8b36627f6676bd1b797728701644f1b59e0c9e05JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13b427e6-f759-61ce-3736-3004f6ef6064&amp;u=a1aHR0cHM6Ly93d3cuZmxhc2hzY29yZS5jb20vdGVubmlzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d2eb253206f4bed3ffde2e104de31fb7e440d97a03c9a81a96931785da028b09JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13b427e6-f759-61ce-3736-3004f6ef6064&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UZW5uaXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=816712d1b9b1d819861479cc11b7f227ce9124e7024900e1c4b50997c06e263aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13b427e6-f759-61ce-3736-3004f6ef6064&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L3Rlbm5pcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ed72de4300da016c57ad1f54a4f47b72907bce08e3dac3601a3168a1eafebccdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13b427e6-f759-61ce-3736-3004f6ef6064&amp;u=a1aHR0cHM6Ly93d3cuYXRwdG91ci5jb20vZW4vdG91cm5hbWVudHM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2b999d6c5d0ee27e6b10ed65f0b9a66ff2c217fd21f7de5c1ac91d8b8b7ef776JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13b427e6-f759-61ce-3736-3004f6ef6064&amp;u=a1aHR0cHM6Ly93d3cuZXNwbi5jb20vdGVubmlzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f2f7566269d54022ef41c9854e7bc7e47c7f15bf02099b9eeb7add30e210e0f5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13b427e6-f759-61ce-3736-3004f6ef6064&amp;u=a1aHR0cHM6Ly93d3cudGVubmlzLmNvbS90b3VybmFtZW50cw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1dae67ea3e34a8020e9918e1ed9f690b3991cb718375248b5f90463489deeedeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13b427e6-f759-61ce-3736-3004f6ef6064&amp;u=a1aHR0cHM6Ly93d3cud3RhdGVubmlzLmNvbS8&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8046812376385cbafc0dbb6dde3f71624aa68843791ec91c2702b2528dbeaee7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a68a693-6b0b-6ba1-1efa-b1716a576a8b&amp;u=a1aHR0cHM6Ly9zcG9ydHMueWFob28uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1d25fbdc30c97b740e31fb3e2d61eea450dcc751b815e0b4c1fbbdc91394f9e7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a68a693-6b0b-6ba1-1efa-b1716a576a8b&amp;u=a1aHR0cHM6Ly9hcG5ld3MuY29tL3Nwb3J0cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=de417f26639a79754440ffbbca5871f639d5eeee2fd75814f4e2b77b78fe141aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a68a693-6b0b-6ba1-1efa-b1716a576a8b&amp;u=a1aHR0cHM6Ly93d3cubXNuLmNvbS9lbi11cy9zcG9ydHM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=71278b1bb6946b04356ff442b79b64b13c41541fb5272d8964d1b6570c4f6c12JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a68a693-6b0b-6ba1-1efa-b1716a576a8b&amp;u=a1aHR0cHM6Ly93d3cuZXNwbi5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2c297ef63b9fe6a0583265db4746343f8aff1e5dbd050e0fae2622ec65f4779bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a68a693-6b0b-6ba1-1efa-b1716a576a8b&amp;u=a1aHR0cHM6Ly93d3cuY2Jzc3BvcnRzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=efd2fdb048f66c4d5cde2bf9573efab6287adac72062f3be4a340d0485cc9c16JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a68a693-6b0b-6ba1-1efa-b1716a576a8b&amp;u=a1aHR0cHM6Ly93d3cuZGVzbW9pbmVzcmVnaXN0ZXIuY29tL3Nwb3J0cy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=405635d6dcadaaae4057d588f0f22ea32dd577e284ace08a314430a971a303d7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a68a693-6b0b-6ba1-1efa-b1716a576a8b&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvbS9zcG9ydA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=80a0c7887ebf8baf68b14bfd302355f0b9aebced58a9107d246d0fec12cca365JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a68a693-6b0b-6ba1-1efa-b1716a576a8b&amp;u=a1aHR0cHM6Ly93d3cuZm94c3BvcnRzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1a569452d2f1c2b80252de80e98bd4b83c7229f48db4ea336fa0608b6eff5aadJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a68a693-6b0b-6ba1-1efa-b1716a576a8b&amp;u=a1aHR0cHM6Ly93d3cudXNhdG9kYXkuY29tL3Nwb3J0cy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9ab315801bfcefa9f12211d2d915ceb2efeb79e877e3c0d3d7b639e931ffb3faJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2bf0941e-398e-6802-3c19-83fc38e46961&amp;u=a1aHR0cHM6Ly93d3cucmVjcmVhdGlvbi5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4344a91dc5c98e07d5c8fea9b8915f1eb80f7e465f984776a895b1f07603a75eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2bf0941e-398e-6802-3c19-83fc38e46961&amp;u=a1aHR0cHM6Ly93d3cuY2l0eW9mZWFzdGxhbnNpbmcuY29tLzI1NzEvUGFya3MtUmVjcmVhdGlvbi1BcnRz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=31ccbdb4e91a30d54143a941d0d3fc66802d139b8377f4fb158a50b261ecc4e0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2bf0941e-398e-6802-3c19-83fc38e46961&amp;u=a1aHR0cHM6Ly9yZWNyZWF0aW9uLnVtaWNoLmVkdS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7aa164342e40497dd8653a393b244b4f4ebc6493b857bf99e3b370e00d81f0d9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2bf0941e-398e-6802-3c19-83fc38e46961&amp;u=a1aHR0cHM6Ly93d3cuY2l0eW9mZWFzdGxhbnNpbmcuY29tLzg2MS9Qcm9ncmFtcy1BY3Rpdml0aWVz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=348903ebdc8ac381ddc6c9083f77e1b5aa41bf9dc0d981eaf2c23d09b6c83b6bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2bf0941e-398e-6802-3c19-83fc38e46961&amp;u=a1aHR0cHM6Ly93d3cucmVjcmVhdGlvbi5nb3YvbG9nLWlu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c33aff270565a178b1140290689cf9ec407f8fbe15eba8e0f8ea048267507362JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2bf0941e-398e-6802-3c19-83fc38e46961&amp;u=a1aHR0cHM6Ly9yZWNzcG9ydHMubXN1LmVkdS9mYWNpbGl0aWVzL3N0dWRlbnQtcmVjcmVhdGlvbi1hbmQtd2VsbG5lc3MtY2VudGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8154a3237f7e4dc5bd7d448416552527963c8c47e5f060e08a6aa267b5871c45JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2bf0941e-398e-6802-3c19-83fc38e46961&amp;u=a1aHR0cHM6Ly93d3cubGFuc2luZy5vcmcvdGhpbmdzLXRvLWRvL291dGRvb3ItcmVjcmVhdGlvbi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2d2654ee547c5167b6914b564bd848523ff8902161d5c6c4cd566872a60999d2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2bf0941e-398e-6802-3c19-83fc38e46961&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvUmVjcmVhdGlvbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9b95b53d15024f7b95e311ae93ac3178f4693c45fab136052439fda514bd12c4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2bf0941e-398e-6802-3c19-83fc38e46961&amp;u=a1aHR0cHM6Ly93d3cubGFuc2luZ21pLmdvdi9wYXJrcy1yZWNyZWF0aW9u&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=05792b1a6019da0c74bcfebeca9784d0ad01b30300d2414cfb0eae137b329fe2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2bf0941e-398e-6802-3c19-83fc38e46961&amp;u=a1aHR0cHM6Ly93d3cubGFuc2luZy5vcmcvdGhpbmdzLXRvLWRvL291dGRvb3ItcmVjcmVhdGlvbi9wYXJrcy1hbmQtZ2FyZGVucy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=94ca0a008d75b22fc99b6c5440853273b6303b316b28e0a5bc4a8904214a4b59JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10d2d0d9-09d6-684b-136c-c73b081869ec&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQzNTk0OTIyNi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=abf6e06739d9d113044ba3c948948210a04ff6beba3d4d6ee092bd2df723dbdfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10d2d0d9-09d6-684b-136c-c73b081869ec&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvWW91dGg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a4b4954dc6549880cd5914aa8c91448471ca22156d03e1882eb0ffc703b64acbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10d2d0d9-09d6-684b-136c-c73b081869ec&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1Yd3VETVNsRXJraw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c7fdd0cbc190f5aafbb32edd69cfa54159ea1f42f1f233d1e393583085b497b6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10d2d0d9-09d6-684b-136c-c73b081869ec&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQzODY5Mzg4OC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e95761bf7c3c85469a960dd25421656d7f5ec17e45f71fe3bb6e25c3fc640096JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10d2d0d9-09d6-684b-136c-c73b081869ec&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3lvdXRo&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e3e735127ab9986bd147c05f117c1b3388017ac5eacf7411e6fbbb20ff640f2fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10d2d0d9-09d6-684b-136c-c73b081869ec&amp;u=a1aHR0cHM6Ly93d3cudHZpbnNpZGVyLmNvbS8xMjg0MDAzL3lvdXRoLXByZW1pZXJlLWRhdGUtdHJhaWxlci1jYXN0LXBsb3Qv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8e468359d90c60697fd25a1345ac4808ce0fd0c2369aa10fa639f092055c8870JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10d2d0d9-09d6-684b-136c-c73b081869ec&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvWW91dGhfKFRWX3Nlcmllcyk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9b96436503cd67f90757f4c23cb311e938ec7dad63a66609886732a2eaa18b5bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10d2d0d9-09d6-684b-136c-c73b081869ec&amp;u=a1aHR0cHM6Ly95b3V0aC5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c25de220324a909b87186897a6d9eedf2d2355623ce0c36b03b8bc89a0a853b4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10d2d0d9-09d6-684b-136c-c73b081869ec&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj0yeGh0Q19pV2NnWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4023d79e9c961cfba6e5269c925ab082302abbd764c4693532bb26f3cca80eb0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10d2d0d9-09d6-684b-136c-c73b081869ec&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3lvdXRo&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=65529e086ff229d190c0e5a8e755645f185655e121a2f7c35176a8435e7f2f66JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=071d25d4-be01-6a9d-1e76-3236bf1c6be2&amp;u=a1aHR0cHM6Ly93d3cubWxiLmNvbS9hdGhsZXRpY3M_bXNvY2tpZD0wNzFkMjVkNGJlMDE2YTlkMWU3NjMyMzZiZjFjNmJlMg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d07aed669968ca248abce95aa8fd0b1fcaa5592ab37350ba3484ce11c9eb2bd8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=071d25d4-be01-6a9d-1e76-3236bf1c6be2&amp;u=a1aHR0cHM6Ly93d3cuYXRobGV0aWMubmV0Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=30d083b6a3a20503623d4250acc1c399af6a5dac72e9902cb8566d25337d84bdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=071d25d4-be01-6a9d-1e76-3236bf1c6be2&amp;u=a1aHR0cHM6Ly93b3JsZGF0aGxldGljcy5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e79630be2cfa3b0fa00e4827fa1edbcdc58d6703900255e3ffa825e945ff7bbcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=071d25d4-be01-6a9d-1e76-3236bf1c6be2&amp;u=a1aHR0cHM6Ly93d3cubnl0aW1lcy5jb20vYXRobGV0aWMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f608af3177bdeb305393b9b530ccfa390ff4f942c624d7fa3f51fcb97a060e4fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=071d25d4-be01-6a9d-1e76-3236bf1c6be2&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQXRobGV0aWNzXyhiYXNlYmFsbCk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3fa57a37877d86247eb43bacdaa77561e752ad7183f01b3b5fb6018d2b377191JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=071d25d4-be01-6a9d-1e76-3236bf1c6be2&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU3BvcnRfb2ZfQXRobGV0aWNz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2bdb184b40084945c69ea039bf93c487a2b8a4cbb96c758c76cd3dbe67572a6bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=071d25d4-be01-6a9d-1e76-3236bf1c6be2&amp;u=a1aHR0cHM6Ly93d3cuZXNwbi5jb20vbWxiL3RlYW0vXy9uYW1lL2F0aC9hdGhsZXRpY3M&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=11cd7f6883811ecc01a5e736b2b8938836c586b908139fc61cd0ab56c76f4a4dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=071d25d4-be01-6a9d-1e76-3236bf1c6be2&amp;u=a1aHR0cHM6Ly93d3cuZXNwbi5jb20vYXRobGV0aWNzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=00ce20e00e01c38477c61923686ace90743539d1ce354f6f4896b52f5b1a6391JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=071d25d4-be01-6a9d-1e76-3236bf1c6be2&amp;u=a1aHR0cHM6Ly93d3cubWxiLmNvbS9hdGhsZXRpY3MvbmV3cz9tc29ja2lkPTA3MWQyNWQ0YmUwMTZhOWQxZTc2MzIzNmJmMWM2YmUy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=36ce9630209e3dfd52cd0ed85b162830c29c5bf381fb350f311401e0b897a94eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=071d25d4-be01-6a9d-1e76-3236bf1c6be2&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc3BvcnRzL2F0aGxldGljcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=34ec9777ef143ec113a2b53820c0d2a4636dc46362006ca64214cca81e6cf598JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08ca7375-81b1-6d99-3342-649780216cd9&amp;u=a1aHR0cHM6Ly93d3cubmZsLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f164ebe59b404ac967ec58e6483e6864220417b45a75375536e8ba2bb1ad949aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08ca7375-81b1-6d99-3342-649780216cd9&amp;u=a1aHR0cHM6Ly93d3cubmZsLmNvbS9uZXdz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7d1a36f90bf429e69aadb8fa1dbbe77aaf3443d72a42285a5b84b095bb9801c6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08ca7375-81b1-6d99-3342-649780216cd9&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Gb290YmFsbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aff7d39857eddb1eaaaaa506cfea2a130641136068f8b86917bce57e5b40d4e5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08ca7375-81b1-6d99-3342-649780216cd9&amp;u=a1aHR0cHM6Ly93d3cuZXNwbi5jb20vbmZsLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=46415c332246cab3c096e71e33b830b09f3f57713319e1de7e2cd0146ab7e7efJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08ca7375-81b1-6d99-3342-649780216cd9&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2Zvb3RiYWxsL3Njb3Jlcy1maXh0dXJlcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=324ca31449c4a39f3b3efe22ce3feb4153ffa908caf39be5050e78aafecdcfe7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08ca7375-81b1-6d99-3342-649780216cd9&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2Zvb3RiYWxs&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d1974867081dee54e28c31915a24d37b31e3ee4500f6ad3a7ba77a2748ada52JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08ca7375-81b1-6d99-3342-649780216cd9&amp;u=a1aHR0cHM6Ly93d3cuc2t5c3BvcnRzLmNvbS9mb290YmFsbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c8a76c636baefe5a62ed2b3dc1dd8de16012dadf532e541f91057825758ea45cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08ca7375-81b1-6d99-3342-649780216cd9&amp;u=a1aHR0cHM6Ly93d3cuY2Jzc3BvcnRzLmNvbS9uZmwv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b29ddb3209f79016a3a13abaa1d1773717388323876a3e9f96309f3963e3ce4bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08ca7375-81b1-6d99-3342-649780216cd9&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9BbWVyaWNhbl9mb290YmFsbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7f1d4080802fbd5490f7fb8f46de3b97f835cb4352e61fd7cff0a3575b665b2bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08ca7375-81b1-6d99-3342-649780216cd9&amp;u=a1aHR0cHM6Ly93d3cuZXNwbi5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5b6c0e448cafc1b11fa91914070e11fc972e3c3165611942ab295850165d2be4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=308cc6ee-4f1b-6924-167e-d10c4ef26847&amp;u=a1aHR0cHM6Ly93d3cuZXNwbi5jb20vc29jY2VyLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a5a41b5cf9b4d6bb78453ad0ce99ae5998a1c39d337796c9190dfe9e4573bde0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=308cc6ee-4f1b-6924-167e-d10c4ef26847&amp;u=a1aHR0cHM6Ly93d3cuZXNwbi5jb20vc29jY2VyL3Njb3JlYm9hcmQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f2e49341d9af1d6bf300166f3a3b8971e81079dcf6c97303020fcc0e2e5f7e3aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=308cc6ee-4f1b-6924-167e-d10c4ef26847&amp;u=a1aHR0cHM6Ly93d3cuZWxnaW55b3V0aHNvY2Nlci5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=71db69311b22984d2b2bcd33710d4097eb9216f36a424faaec027adc1fdde32fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=308cc6ee-4f1b-6924-167e-d10c4ef26847&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Bc3NvY2lhdGlvbl9mb290YmFsbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=03aeb80bc02cc67df12df3754d7de4026ccd9615d4330f67172484f72eaf8111JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=308cc6ee-4f1b-6924-167e-d10c4ef26847&amp;u=a1aHR0cHM6Ly93d3cubGl2ZXNjb3JlLmNvbS9lbi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2f3656758c418b06af68c8fe7cbb050fc6b6268d4c654468a6ca7429b6d14006JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=308cc6ee-4f1b-6924-167e-d10c4ef26847&amp;u=a1aHR0cHM6Ly93d3cuZmxhc2hzY29yZS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=22e88547ad14467013d223e1edcca243bf79a5d16d97c0beb2cd1a0935b62024JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=308cc6ee-4f1b-6924-167e-d10c4ef26847&amp;u=a1aHR0cHM6Ly93d3cuZmlmYS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7596decf891b35d62cf0b8edf147b82845548d9764b198011a2c086f51f4d73aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=308cc6ee-4f1b-6924-167e-d10c4ef26847&amp;u=a1aHR0cHM6Ly93d3cubWxzc29jY2VyLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eef298d72e5674017e2401eeb6c052bccd5cf1cd879f91209c3a406797acafd1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=308cc6ee-4f1b-6924-167e-d10c4ef26847&amp;u=a1aHR0cHM6Ly91cy5zb2NjZXJ3YXkuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=69d3cf857d4cf84862f9a6a708c2353791131c009e9bee71e06456e57f0d190dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=308cc6ee-4f1b-6924-167e-d10c4ef26847&amp;u=a1aHR0cHM6Ly93d3cuYmVzb2NjZXIuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9f6546fc8582983f83f69c7f8a27051a506178f5d01702173e1bf43bb8273270JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3a6b23ac-fc5e-61af-173c-344efd4b60dd&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvUnVnYnlfdW5pb24&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5fff7153d6f713f92ba471d66518fb90e62c8793bf738e2ca2bc8daf798e81deJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3a6b23ac-fc5e-61af-173c-344efd4b60dd&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc3BvcnRzL3J1Z2J5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3322fd22ddf3ea9fec582f23edb8f82d3458b454c471548b0715410a424d188fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3a6b23ac-fc5e-61af-173c-344efd4b60dd&amp;u=a1aHR0cHM6Ly93d3cud29ybGQucnVnYnkv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=017db453bf47639a1230a6b0897b53c502bb36eb408932162d05f63edcc94602JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3a6b23ac-fc5e-61af-173c-344efd4b60dd&amp;u=a1aHR0cHM6Ly93d3cud29ybGQucnVnYnkvdG91cm5hbWVudHMvZml4dHVyZXMtcmVzdWx0cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=45868abbb7324854ba0b15a7f61286e693f0162c3322f7d7525f070a15c8498eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3a6b23ac-fc5e-61af-173c-344efd4b60dd&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L3J1Z2J5LXVuaW9u&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=120f8209e45b70ad274af4c862d79f90927be7e19323ca69ce36f2c459f96f2cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3a6b23ac-fc5e-61af-173c-344efd4b60dd&amp;u=a1aHR0cHM6Ly91c2EucnVnYnkvcnVnYnkxMDE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c8090810e0221ae8f0bb819601ddd24bce3af772bb68c59987f85b7a13e81deaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3a6b23ac-fc5e-61af-173c-344efd4b60dd&amp;u=a1aHR0cHM6Ly9zdXBlcnNwb3J0LmNvbS9ydWdieS9maXh0dXJlcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7a8a3ba1470aa162877d362b4ba03ab5d08e3e52b957379596eadac239a44735JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3a6b23ac-fc5e-61af-173c-344efd4b60dd&amp;u=a1aHR0cHM6Ly93d3cucGxhbmV0cnVnYnkuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2e1b65bab21cbe181f54dcf84eb7ef43078ad25a1a1bee6b54f18e4337bc7278JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3a6b23ac-fc5e-61af-173c-344efd4b60dd&amp;u=a1aHR0cHM6Ly93d3cucnVnYnlwYXNzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c2e52d2d3036cffc4f30c8e18bd302b7b0637707b7ef1d6a9c6c2f10b04ab0bdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3a6b23ac-fc5e-61af-173c-344efd4b60dd&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L3J1Z2J5LXVuaW9uL3Njb3Jlcy1maXh0dXJlcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=47629279320a2d1047e90f2239cedf0666ab04efca2f565c21f5ffe2bc7a5d1eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3afbee61-0fad-676d-0d71-f9830e366606&amp;u=a1aHR0cHM6Ly93d3cuY3JpY2tldHdpcmVsZXNzLmNvbS8_bXNvY2tpZD0zYWZiZWU2MTBmYWQ2NzZkMGQ3MWY5ODMwZTM2NjYwNg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=782a5d0779c4617dd8a309aae9ffef950ba242dcdb07c17e3c492a5e826ae4bfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3afbee61-0fad-676d-0d71-f9830e366606&amp;u=a1aHR0cHM6Ly93d3cuY3JpY2luZm8uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c8984b7cc6ad3ff06f59654276ade4e00609e0947cb3134c724ed324deece4feJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3afbee61-0fad-676d-0d71-f9830e366606&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ3JpY2tldA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9306df0b5066dcadc946f5ad97159fce8ae23933076b7837a42bdd8bdd0ddd0eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3afbee61-0fad-676d-0d71-f9830e366606&amp;u=a1aHR0cHM6Ly93d3cuY3JpY2luZm8uY29tL2xpdmUtY3JpY2tldC1zY29yZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4ed7b24eb2fc7587a34953faf03df1754485798cc413ec91ce34e46cfe5c3f12JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3afbee61-0fad-676d-0d71-f9830e366606&amp;u=a1aHR0cHM6Ly93d3cuY3JpY2tldHdpcmVsZXNzLmNvbS9xdWlja3BheS5odG1sP21zb2NraWQ9M2FmYmVlNjEwZmFkNjc2ZDBkNzFmOTgzMGUzNjY2MDY&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a72b679fdfe53d8dbccaeb816022143f92ffc7f01d43140a627808a9f58b5451JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3afbee61-0fad-676d-0d71-f9830e366606&amp;u=a1aHR0cHM6Ly9kb29kbGVjcmlja2V0Lm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1b2ad98bf87e9879d23e4d24e174539aac8946cf21e87cee7ef55cc98ac0c44dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3afbee61-0fad-676d-0d71-f9830e366606&amp;u=a1aHR0cHM6Ly93d3cuZXNwbi5jb20vY3JpY2tldC9zY29yZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5ade332d4d0782654f1930bf39ba99af94e9a1b75de7d310b5bb1ea4b3599e77JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3afbee61-0fad-676d-0d71-f9830e366606&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2NyaWNrZXQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=062a6ace8e581ac369db2ae1a082bc2942b56008180cc3de722eb38c80f7c283JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3afbee61-0fad-676d-0d71-f9830e366606&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc3BvcnRzL2NyaWNrZXQtc3BvcnQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3c51237f708f6cdee9b42cf05688aa35e89f78f88588a64e2f1804f86ccf9338JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3afbee61-0fad-676d-0d71-f9830e366606&amp;u=a1aHR0cHM6Ly93d3cuY3JpY2tldC5jb20uYXUv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2a2e80b3a834da9b9193dea280f5d355a22541bba97a4c25c9129e818dcfb73dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02e695f6-5c75-690b-1c3a-82145db1687a&amp;u=a1aHR0cHM6Ly93d3cuc3RwYXVsLmdvdi9kZXBhcnRtZW50cy9wYXJrcy1hbmQtcmVjcmVhdGlvbi9hcXVhdGljcy9zd2ltbWluZy1sZXNzb25z&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=885f0a40e39d16d9f57d8c0d36a3cb41e63519195c5f39bf443b163610cb0fc7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02e695f6-5c75-690b-1c3a-82145db1687a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Td2ltbWluZw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8cbe4dbdd8e718596bed191f061ed8cc7a344b94502865e7380169ece66fc7a0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02e695f6-5c75-690b-1c3a-82145db1687a&amp;u=a1aHR0cHM6Ly93d3cuc3RwYXVsLmdvdi9kZXBhcnRtZW50cy9wYXJrcy1hbmQtcmVjcmVhdGlvbi9hcXVhdGljcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5c54380aeb9a7012b5bbf1183d11b22c60cd08ac0939a84873f5b8302deb33b0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02e695f6-5c75-690b-1c3a-82145db1687a&amp;u=a1aHR0cHM6Ly93d3cuZm9zc3N3aW1zY2hvb2wuY29tL3N3aW1taW5nLWxlc3Nvbi1sb2NhdGlvbnMvc3QtcGF1bC1taW5uZXNvdGEtNTUxMDQv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=99ef958358b498daac979eb823f708a71b41a3272a5aba0b5ee3b75e7eaf8098JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02e695f6-5c75-690b-1c3a-82145db1687a&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc3BvcnRzL3N3aW1taW5nLXNwb3J0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d6fa5fa7bbbc4b0df644ccca4722e1a6f7ccc2634b3454d6434ba61ebd1dcc09JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02e695f6-5c75-690b-1c3a-82145db1687a&amp;u=a1aHR0cHM6Ly93d3cuZ29tb3Rpb25hcHAuY29tL3RlYW0vbW5zc2MvcGFnZS9ob21l&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=185a0c9c53537727f84a3c44567f3b91841b0f7062028731b278312df62bf823JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02e695f6-5c75-690b-1c3a-82145db1687a&amp;u=a1aHR0cHM6Ly90d2luY2l0aWVzZmFtaWx5LmNvbS93YXRlci1wYXJrcy1wb29scy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1472a4604d56605b4b639777f7bb0d6c3adad6412b37331e8a5171010366020cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02e695f6-5c75-690b-1c3a-82145db1687a&amp;u=a1aHR0cHM6Ly93d3cuZmFtaWx5ZnVudHdpbmNpdGllcy5jb20vdHdpbi1jaXRpZXMtaW5kb29yLXdhdGVycGFya3Mv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f56579ecec553c47cb70d1bf0f43fe2ca0a64b3d94b99f74768dc3556aed4423JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02e695f6-5c75-690b-1c3a-82145db1687a&amp;u=a1aHR0cHM6Ly9yZWN3ZWxsLnVtbi5lZHUvY29tbXVuaXR5LXlvdXRoL2dvcGhlci1zd2ltLXNjaG9vbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=df4daaab8f09f33d16a4d0d75e5a9c719ee4870d00d0e6b06aa867153dfad715JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02e695f6-5c75-690b-1c3a-82145db1687a&amp;u=a1aHR0cHM6Ly9taW5uZXNvdGFqY2Mub3JnL2FxdWF0aWNz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a0395e13c75d51e0401db0559748c58c810cb69deefeba3c141c1c136c9c9498JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ddafcc-e936-6825-092b-b82ee8ed69dc&amp;u=a1aHR0cHM6Ly93d3cudGVubmlzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=02be25d3f7217e0173fcaaabb83dc47b277855fe7d689a12ec4ef0fbea4528dfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ddafcc-e936-6825-092b-b82ee8ed69dc&amp;u=a1aHR0cHM6Ly93d3cuZXNwbi5jb20vdGVubmlzL3Njb3JlYm9hcmQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9a22e68fd562be70f04d2ae5cdd05524d5f38272e6648f6bb763e6f1f4b4037eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ddafcc-e936-6825-092b-b82ee8ed69dc&amp;u=a1aHR0cHM6Ly93d3cuYXRwdG91ci5jb20vZW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1c19fabbdd12354c6adf100ba678501c82a65acab0d49d38fd07550c66b4fff1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ddafcc-e936-6825-092b-b82ee8ed69dc&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UZW5uaXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=17b5772a1dfdb5a964a6f9e34c2a69360d7ef501fc76c14e86d797c4526edcd5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ddafcc-e936-6825-092b-b82ee8ed69dc&amp;u=a1aHR0cHM6Ly93d3cuZmxhc2hzY29yZS5jb20vdGVubmlzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4d1e30239f77a0dd6b33278b0d7ad5bb6aaad6ba1bf0f861a3dd5520c835a2c6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ddafcc-e936-6825-092b-b82ee8ed69dc&amp;u=a1aHR0cHM6Ly93d3cuZXNwbi5jb20vdGVubmlzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4f7ea87a96fc4743e92fbb512a1771a14e64a5aeeee0603ccb3a5476344fc459JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ddafcc-e936-6825-092b-b82ee8ed69dc&amp;u=a1aHR0cHM6Ly93d3cuYXRwdG91ci5jb20vZW4vdG91cm5hbWVudHM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=878b937595c2fde723a582af9c206f092b9435056ce6044aed437e5fd8a5d443JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ddafcc-e936-6825-092b-b82ee8ed69dc&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L3Rlbm5pcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f35b016fc4f8c6678d00cf0d7ff311fe5fd9fe85bf1b545c664c8030a1c70c4cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ddafcc-e936-6825-092b-b82ee8ed69dc&amp;u=a1aHR0cHM6Ly93d3cudGVubmlzLmNvbS90b3VybmFtZW50cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9dc2bc0628db504019778efa72dbc47bd5307d3c2e372aff7a91cd79643ffedbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ddafcc-e936-6825-092b-b82ee8ed69dc&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L3Rlbm5pcy9zY29yZXMtYW5kLXNjaGVkdWxl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=469488953f2f486cdf93e600620908c979f5f9a3b931c65069c734d66fcbd1bbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013e53be-9fab-672d-0204-445c9e7f6617&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vY2hyb21lL2Fuc3dlci85NTM0Nj9obD1lbiZjbz1HRU5JRS5QbGF0Zm9ybSUzRERlc2t0b3A&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7410e9b7b2afd20ec907698a00e8ce86c04133bd7a28165df446c8f9ce852d2eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013e53be-9fab-672d-0204-445c9e7f6617&amp;u=a1aHR0cHM6Ly9zdGFja292ZXJmbG93LmNvbS9xdWVzdGlvbnMvOTMyMzkzNi9jaHJvbWUtd2ViLXN0b3Jl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=611f2b92310160f6d613c8c15287d4046dd5cf2375c7682d6e367d647084915eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013e53be-9fab-672d-0204-445c9e7f6617&amp;u=a1aHR0cHM6Ly9zdGFja292ZXJmbG93LmNvbS9xdWVzdGlvbnMvNzkzNjI3Ny9ob3ctdG8tbGluay10by1jaHJvbWUtZXh0ZW5zaW9uLWxpa2UtY2hyb21lLXdlYi1zdG9yZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dbecd1330ca316ef0dfc7d141e24dbd46780c97d320c54cf34f15a929afcd824JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013e53be-9fab-672d-0204-445c9e7f6617&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vY2hyb21lX3dlYnN0b3JlL2Fuc3dlci8xMDUzMzQ2P2hsPWVu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1c227d1dceca9591952a6c1cf672f14db45bfb2600e3915da98034b55c450118JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013e53be-9fab-672d-0204-445c9e7f6617&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vY2hyb21lX3dlYnN0b3JlL2Fuc3dlci8yNjY0NzY5P2hsPWph&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0fc68dfa7d564cff7b9a11212bdba118eb3cc6e8ab89c1e322e17a3f6e88804eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013e53be-9fab-672d-0204-445c9e7f6617&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vY2hyb21lLz9obD1lbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d2f30a13bef7639920decfbf62182b313642dde6ffc344ab589636f553b76991JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013e53be-9fab-672d-0204-445c9e7f6617&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vY2hyb21lX3dlYnN0b3JlL2Fuc3dlci8yNjY0NzY5P2hsPWVuLUdC&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bfec6433a0a80ca2afccf0f5b99d65999f97539036ff6a611fd545eb4b0639faJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013e53be-9fab-672d-0204-445c9e7f6617&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vY2hyb21lL2Fuc3dlci85NTM0Nj9obD1wdC00MTkmY289R0VOSUUuUGxhdGZvcm0lM0REZXNrdG9w&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2a5f70b37180532a32813e2021d9017a8c10d76831856599089e55bfe68cae07JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013e53be-9fab-672d-0204-445c9e7f6617&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vY2hyb21lX3dlYnN0b3JlL2Fuc3dlci8xMDQ3Nzc2P2hsPWVu&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
+  </si>
+  <si>
+    <t>Salt River</t>
   </si>
   <si>
     <t>Bing</t>
@@ -994,7 +1045,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1028,19 +1079,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="G2" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H2" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1048,19 +1099,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="G3" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H3" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1068,19 +1119,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="G4" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H4" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1088,19 +1139,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="G5" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H5" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1108,19 +1159,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="G6" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H6" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1128,19 +1179,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G7" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H7" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1148,19 +1199,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="G8" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H8" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1168,19 +1219,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="G9" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H9" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1188,19 +1239,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="G10" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H10" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1208,19 +1259,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="G11" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H11" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1228,19 +1279,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G12" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H12" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1248,19 +1299,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="G13" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H13" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1268,19 +1319,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="G14" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H14" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1288,19 +1339,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G15" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H15" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1308,19 +1359,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C16" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="G16" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H16" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1328,19 +1379,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C17" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G17" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H17" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1348,19 +1399,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="G18" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H18" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1368,19 +1419,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G19" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H19" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1388,19 +1439,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="G20" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H20" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1408,19 +1459,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="G21" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H21" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1428,19 +1479,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="G22" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H22" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1448,19 +1499,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="G23" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H23" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1468,19 +1519,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="G24" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H24" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1488,19 +1539,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C25" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="G25" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H25" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1508,19 +1559,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="G26" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H26" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1528,19 +1579,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G27" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H27" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1548,19 +1599,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G28" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H28" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1568,19 +1619,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C29" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G29" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H29" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1588,19 +1639,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C30" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G30" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H30" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1608,19 +1659,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C31" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="G31" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H31" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1628,19 +1679,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C32" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="G32" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H32" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1648,19 +1699,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="G33" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H33" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1668,19 +1719,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="G34" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H34" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1688,19 +1739,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="G35" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H35" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1708,19 +1759,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C36" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="G36" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H36" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1728,19 +1779,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C37" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="G37" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H37" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1748,19 +1799,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C38" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="G38" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H38" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1768,19 +1819,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C39" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="G39" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H39" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1788,19 +1839,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C40" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="G40" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H40" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1808,19 +1859,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C41" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G41" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H41" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1828,19 +1879,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C42" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G42" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H42" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1848,19 +1899,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C43" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G43" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H43" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1868,19 +1919,19 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C44" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G44" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H44" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1888,19 +1939,19 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C45" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="G45" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H45" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1908,19 +1959,19 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C46" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="G46" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H46" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1928,19 +1979,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C47" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G47" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H47" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1948,19 +1999,19 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C48" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="G48" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H48" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1968,19 +2019,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C49" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="G49" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H49" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1988,19 +2039,19 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C50" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="G50" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H50" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -2008,19 +2059,19 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C51" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="G51" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H51" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -2028,19 +2079,19 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C52" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="G52" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H52" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -2048,19 +2099,19 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C53" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="G53" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H53" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -2068,19 +2119,19 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C54" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="G54" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H54" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2088,19 +2139,19 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C55" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="G55" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H55" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2108,19 +2159,19 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C56" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="G56" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H56" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2128,19 +2179,19 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C57" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G57" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H57" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2148,19 +2199,19 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C58" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="G58" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H58" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2168,19 +2219,19 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C59" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="G59" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H59" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2188,19 +2239,19 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C60" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="G60" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H60" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2208,19 +2259,19 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C61" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="G61" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H61" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2228,19 +2279,19 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C62" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="G62" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H62" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2248,19 +2299,19 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C63" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="G63" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H63" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2268,19 +2319,19 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C64" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="G64" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H64" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2288,19 +2339,19 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C65" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="G65" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H65" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2308,19 +2359,19 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C66" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="G66" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H66" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2328,19 +2379,19 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C67" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="G67" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H67" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2348,19 +2399,19 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C68" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="G68" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H68" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2368,19 +2419,19 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C69" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="G69" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H69" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2388,19 +2439,19 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C70" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="G70" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H70" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2408,19 +2459,19 @@
         <v>77</v>
       </c>
       <c r="B71" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C71" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="G71" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H71" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2428,19 +2479,19 @@
         <v>78</v>
       </c>
       <c r="B72" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C72" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="G72" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H72" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2448,19 +2499,19 @@
         <v>79</v>
       </c>
       <c r="B73" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C73" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G73" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H73" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2468,19 +2519,19 @@
         <v>80</v>
       </c>
       <c r="B74" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C74" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="G74" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H74" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -2488,19 +2539,19 @@
         <v>81</v>
       </c>
       <c r="B75" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C75" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="G75" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H75" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -2508,19 +2559,19 @@
         <v>82</v>
       </c>
       <c r="B76" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C76" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="G76" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H76" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2528,19 +2579,19 @@
         <v>83</v>
       </c>
       <c r="B77" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C77" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="G77" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H77" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -2548,19 +2599,19 @@
         <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C78" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="G78" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H78" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -2568,19 +2619,19 @@
         <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C79" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="G79" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H79" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -2588,19 +2639,19 @@
         <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C80" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="G80" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H80" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -2608,19 +2659,19 @@
         <v>87</v>
       </c>
       <c r="B81" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C81" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="G81" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H81" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -2628,19 +2679,19 @@
         <v>88</v>
       </c>
       <c r="B82" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C82" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="G82" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H82" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -2648,19 +2699,19 @@
         <v>89</v>
       </c>
       <c r="B83" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C83" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="G83" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H83" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -2668,19 +2719,19 @@
         <v>90</v>
       </c>
       <c r="B84" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C84" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="G84" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H84" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -2688,19 +2739,19 @@
         <v>91</v>
       </c>
       <c r="B85" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C85" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="G85" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H85" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -2708,19 +2759,19 @@
         <v>92</v>
       </c>
       <c r="B86" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C86" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="G86" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H86" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -2728,19 +2779,19 @@
         <v>93</v>
       </c>
       <c r="B87" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C87" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="G87" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H87" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -2748,19 +2799,19 @@
         <v>94</v>
       </c>
       <c r="B88" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C88" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G88" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H88" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -2768,19 +2819,19 @@
         <v>95</v>
       </c>
       <c r="B89" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C89" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="G89" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H89" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -2788,19 +2839,19 @@
         <v>96</v>
       </c>
       <c r="B90" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C90" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="G90" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H90" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -2808,19 +2859,19 @@
         <v>97</v>
       </c>
       <c r="B91" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C91" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="G91" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H91" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -2828,19 +2879,19 @@
         <v>98</v>
       </c>
       <c r="B92" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C92" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="G92" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H92" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -2848,19 +2899,19 @@
         <v>99</v>
       </c>
       <c r="B93" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C93" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="G93" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H93" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -2868,19 +2919,19 @@
         <v>100</v>
       </c>
       <c r="B94" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C94" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="G94" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H94" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -2888,19 +2939,19 @@
         <v>101</v>
       </c>
       <c r="B95" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C95" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="G95" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H95" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -2908,19 +2959,19 @@
         <v>102</v>
       </c>
       <c r="B96" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C96" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G96" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H96" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -2928,19 +2979,19 @@
         <v>103</v>
       </c>
       <c r="B97" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C97" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G97" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H97" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -2948,19 +2999,19 @@
         <v>104</v>
       </c>
       <c r="B98" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C98" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="G98" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H98" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -2968,19 +3019,19 @@
         <v>105</v>
       </c>
       <c r="B99" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C99" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="G99" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H99" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -2988,19 +3039,19 @@
         <v>106</v>
       </c>
       <c r="B100" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C100" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="G100" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="H100" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -3008,19 +3059,179 @@
         <v>107</v>
       </c>
       <c r="B101" t="s">
+        <v>116</v>
+      </c>
+      <c r="C101" t="s">
+        <v>117</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="G101" t="s">
+        <v>227</v>
+      </c>
+      <c r="H101" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" t="s">
         <v>108</v>
       </c>
-      <c r="C101" t="s">
+      <c r="B102" t="s">
+        <v>116</v>
+      </c>
+      <c r="C102" t="s">
+        <v>117</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G102" t="s">
+        <v>227</v>
+      </c>
+      <c r="H102" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" t="s">
         <v>109</v>
       </c>
-      <c r="F101" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="G101" t="s">
-        <v>210</v>
-      </c>
-      <c r="H101" t="s">
-        <v>211</v>
+      <c r="B103" t="s">
+        <v>116</v>
+      </c>
+      <c r="C103" t="s">
+        <v>117</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="G103" t="s">
+        <v>227</v>
+      </c>
+      <c r="H103" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" t="s">
+        <v>110</v>
+      </c>
+      <c r="B104" t="s">
+        <v>116</v>
+      </c>
+      <c r="C104" t="s">
+        <v>117</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G104" t="s">
+        <v>227</v>
+      </c>
+      <c r="H104" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" t="s">
+        <v>111</v>
+      </c>
+      <c r="B105" t="s">
+        <v>116</v>
+      </c>
+      <c r="C105" t="s">
+        <v>117</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G105" t="s">
+        <v>227</v>
+      </c>
+      <c r="H105" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" t="s">
+        <v>112</v>
+      </c>
+      <c r="B106" t="s">
+        <v>116</v>
+      </c>
+      <c r="C106" t="s">
+        <v>117</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G106" t="s">
+        <v>227</v>
+      </c>
+      <c r="H106" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" t="s">
+        <v>113</v>
+      </c>
+      <c r="B107" t="s">
+        <v>116</v>
+      </c>
+      <c r="C107" t="s">
+        <v>117</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G107" t="s">
+        <v>227</v>
+      </c>
+      <c r="H107" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" t="s">
+        <v>114</v>
+      </c>
+      <c r="B108" t="s">
+        <v>116</v>
+      </c>
+      <c r="C108" t="s">
+        <v>117</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G108" t="s">
+        <v>227</v>
+      </c>
+      <c r="H108" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" t="s">
+        <v>115</v>
+      </c>
+      <c r="B109" t="s">
+        <v>116</v>
+      </c>
+      <c r="C109" t="s">
+        <v>117</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G109" t="s">
+        <v>227</v>
+      </c>
+      <c r="H109" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -3125,6 +3336,14 @@
     <hyperlink ref="F99" r:id="rId98"/>
     <hyperlink ref="F100" r:id="rId99"/>
     <hyperlink ref="F101" r:id="rId100"/>
+    <hyperlink ref="F102" r:id="rId101"/>
+    <hyperlink ref="F103" r:id="rId102"/>
+    <hyperlink ref="F104" r:id="rId103"/>
+    <hyperlink ref="F105" r:id="rId104"/>
+    <hyperlink ref="F106" r:id="rId105"/>
+    <hyperlink ref="F107" r:id="rId106"/>
+    <hyperlink ref="F108" r:id="rId107"/>
+    <hyperlink ref="F109" r:id="rId108"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
